--- a/AtchisonRegime/Outputs/USA/USA_Size_Tilt/df_regEquityReturns_USA_Size_Tilt.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Size_Tilt/df_regEquityReturns_USA_Size_Tilt.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6913,7 +6913,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C114" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D114" t="b">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C115" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D115" t="b">
         <v>0</v>
@@ -7027,7 +7027,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C116" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D116" t="b">
         <v>0</v>
@@ -7084,7 +7084,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D117" t="b">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C118" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D118" t="b">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D119" t="b">
         <v>0</v>
@@ -7255,7 +7255,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D120" t="b">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D121" t="b">
         <v>0</v>
@@ -7369,7 +7369,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D122" t="b">
         <v>0</v>
@@ -7423,10 +7423,10 @@
         <v>45716</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C123" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D123" t="b">
         <v>0</v>
@@ -7480,10 +7480,10 @@
         <v>45747</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D124" t="b">
         <v>0</v>
@@ -7529,6 +7529,63 @@
         <v>133.5447987073289</v>
       </c>
       <c r="Q124" t="n">
+        <v>123.2616527373862</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B125" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" t="b">
+        <v>1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-8.47616175672427</v>
+      </c>
+      <c r="G125" t="n">
+        <v>322848.9418052674</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-8.47616175672427</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>122.8557588915285</v>
+      </c>
+      <c r="O125" t="n">
+        <v>155.8497951536329</v>
+      </c>
+      <c r="P125" t="n">
+        <v>133.5447987073289</v>
+      </c>
+      <c r="Q125" t="n">
         <v>123.2616527373862</v>
       </c>
     </row>
